--- a/data/trans_dic/P19C09-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19C09-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por otros motivos</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por otros motivos (tasa de respuesta: 99,04%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,17</t>
+          <t>2,45; 5,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,34</t>
+          <t>0,95; 3,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,93</t>
+          <t>1,79; 4,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,69; 6,41</t>
+          <t>3,73; 6,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,08</t>
+          <t>2,02; 4,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,14</t>
+          <t>2,29; 5,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,51; 5,41</t>
+          <t>3,46; 5,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,42</t>
+          <t>1,84; 3,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 4,52</t>
+          <t>2,4; 4,41</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,48</t>
+          <t>1,66; 3,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,94</t>
+          <t>0,79; 1,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,82</t>
+          <t>2,16; 3,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,65</t>
+          <t>1,15; 2,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,53</t>
+          <t>1,85; 3,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,65</t>
+          <t>1,3; 2,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 2,82</t>
+          <t>1,56; 2,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,48</t>
+          <t>1,42; 2,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 2,97</t>
+          <t>1,89; 3,06</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,11</t>
+          <t>0,77; 3,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 5,61</t>
+          <t>1,83; 5,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,52</t>
+          <t>1,48; 4,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 5,76</t>
+          <t>2,02; 6,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,71</t>
+          <t>1,87; 5,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 6,71</t>
+          <t>2,7; 6,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,92</t>
+          <t>1,68; 3,98</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,7</t>
+          <t>2,14; 4,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 4,79</t>
+          <t>2,39; 4,81</t>
         </is>
       </c>
     </row>
@@ -1013,22 +1013,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,3</t>
+          <t>1,23; 2,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 3,61</t>
+          <t>2,3; 3,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 3,9</t>
+          <t>2,51; 3,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,19; 3,52</t>
+          <t>2,24; 3,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,17 +1038,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 3,43</t>
+          <t>2,45; 3,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 2,72</t>
+          <t>1,91; 2,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 3,23</t>
+          <t>2,33; 3,21</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo motivo por su última visita al dentista fue por otros motivos</t>
+          <t>Población cuyo motivo por su última visita al dentista fue por otros motivos (tasa de respuesta: 99,04%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16920; 35585</t>
+          <t>16893; 35890</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8013; 25605</t>
+          <t>7304; 23879</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7729; 22544</t>
+          <t>8169; 21846</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35348; 61492</t>
+          <t>35745; 61379</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>22406; 45368</t>
+          <t>22485; 46830</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13572; 32835</t>
+          <t>14659; 32785</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>57877; 89072</t>
+          <t>57026; 90434</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>34424; 64129</t>
+          <t>34492; 63503</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25564; 49605</t>
+          <t>26289; 48359</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21307; 45605</t>
+          <t>21824; 46072</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12532; 31787</t>
+          <t>12940; 32195</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36013; 64859</t>
+          <t>36624; 66328</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15487; 36281</t>
+          <t>15815; 36455</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28760; 54412</t>
+          <t>28566; 55746</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22786; 45290</t>
+          <t>22180; 45854</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42822; 75522</t>
+          <t>41715; 72755</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>45837; 78794</t>
+          <t>45142; 78586</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>64605; 101012</t>
+          <t>64463; 104224</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2876; 14032</t>
+          <t>3451; 15742</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7035; 23902</t>
+          <t>7794; 23554</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7374; 22561</t>
+          <t>7398; 23161</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7775; 23497</t>
+          <t>8218; 25672</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7356; 23539</t>
+          <t>7727; 22843</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13566; 34113</t>
+          <t>13702; 33423</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13840; 33685</t>
+          <t>14427; 34158</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17602; 39415</t>
+          <t>17970; 39990</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>24203; 48221</t>
+          <t>24105; 48492</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>49747; 80395</t>
+          <t>49811; 80461</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>36061; 65157</t>
+          <t>34796; 63611</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61486; 95891</t>
+          <t>61100; 94582</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69534; 106829</t>
+          <t>68707; 105070</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>67139; 107951</t>
+          <t>68651; 108373</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>59980; 95819</t>
+          <t>59923; 95973</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>126092; 178096</t>
+          <t>127168; 175380</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>112286; 160284</t>
+          <t>112826; 161484</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>127493; 177927</t>
+          <t>128331; 176754</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19C09-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19C09-Estudios-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,21</t>
+          <t>2,34; 5,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 3,12</t>
+          <t>1,02; 3,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,78</t>
+          <t>1,73; 4,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,73; 6,4</t>
+          <t>3,66; 6,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,21</t>
+          <t>2,04; 4,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,13</t>
+          <t>2,24; 5,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,46; 5,49</t>
+          <t>3,53; 5,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 3,38</t>
+          <t>1,86; 3,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,4; 4,41</t>
+          <t>2,36; 4,58</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,51</t>
+          <t>1,64; 3,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 1,96</t>
+          <t>0,78; 2,0</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 3,91</t>
+          <t>2,15; 3,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 2,66</t>
+          <t>1,12; 2,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 3,61</t>
+          <t>1,84; 3,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,68</t>
+          <t>1,26; 2,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,71</t>
+          <t>1,59; 2,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,47</t>
+          <t>1,46; 2,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,06</t>
+          <t>1,89; 2,93</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,49</t>
+          <t>0,6; 3,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,53</t>
+          <t>1,71; 5,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,64</t>
+          <t>1,34; 4,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 6,3</t>
+          <t>1,93; 6,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,54</t>
+          <t>1,83; 5,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,7; 6,58</t>
+          <t>2,68; 6,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,98</t>
+          <t>1,59; 3,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,77</t>
+          <t>2,14; 4,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,81</t>
+          <t>2,49; 4,81</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,28</t>
+          <t>2,03; 3,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,25</t>
+          <t>1,26; 2,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 3,56</t>
+          <t>2,3; 3,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 3,84</t>
+          <t>2,54; 3,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 3,53</t>
+          <t>2,24; 3,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,36</t>
+          <t>2,1; 3,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,38</t>
+          <t>2,44; 3,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 2,74</t>
+          <t>1,9; 2,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 3,21</t>
+          <t>2,33; 3,27</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>16893; 35890</t>
+          <t>16132; 35739</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7304; 23879</t>
+          <t>7789; 25282</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8169; 21846</t>
+          <t>7926; 21477</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35745; 61379</t>
+          <t>35067; 61648</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>22485; 46830</t>
+          <t>22674; 45652</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14659; 32785</t>
+          <t>14339; 34243</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>57026; 90434</t>
+          <t>58100; 90120</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>34492; 63503</t>
+          <t>34894; 63973</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26289; 48359</t>
+          <t>25880; 50181</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21824; 46072</t>
+          <t>21504; 47030</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12940; 32195</t>
+          <t>12837; 32761</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36624; 66328</t>
+          <t>36410; 64836</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15815; 36455</t>
+          <t>15398; 35464</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28566; 55746</t>
+          <t>28428; 55217</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22180; 45854</t>
+          <t>21487; 46724</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41715; 72755</t>
+          <t>42564; 73744</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>45142; 78586</t>
+          <t>46431; 79569</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>64463; 104224</t>
+          <t>64326; 99655</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3451; 15742</t>
+          <t>2702; 14480</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7794; 23554</t>
+          <t>7261; 23478</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7398; 23161</t>
+          <t>6706; 22621</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8218; 25672</t>
+          <t>7885; 24591</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7727; 22843</t>
+          <t>7547; 23434</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13702; 33423</t>
+          <t>13639; 32241</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14427; 34158</t>
+          <t>13695; 33207</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17970; 39990</t>
+          <t>17932; 39680</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>24105; 48492</t>
+          <t>25069; 48453</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>49811; 80461</t>
+          <t>49727; 81908</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>34796; 63611</t>
+          <t>35566; 66818</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61100; 94582</t>
+          <t>60991; 95449</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>68707; 105070</t>
+          <t>69568; 105202</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>68651; 108373</t>
+          <t>68636; 106160</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>59923; 95973</t>
+          <t>60045; 96129</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>127168; 175380</t>
+          <t>126470; 175335</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>112826; 161484</t>
+          <t>112086; 159629</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>128331; 176754</t>
+          <t>128549; 180379</t>
         </is>
       </c>
     </row>
